--- a/jogos_2025-05-19.xlsx
+++ b/jogos_2025-05-19.xlsx
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Inđija</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.67</v>
+        <v>3.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
-        <v>4.42</v>
+        <v>4.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.72</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.98</v>
       </c>
-      <c r="T5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1119,20 +1119,20 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.67</v>
+        <v>2.22</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45796.5</v>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inđija</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.8</v>
+        <v>2.67</v>
       </c>
       <c r="M6" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y6" t="n">
         <v>3.21</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.37</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AI6" t="n">
-        <v>2.22</v>
+        <v>2.67</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45796.5</v>
@@ -1288,19 +1288,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sloven Ruma</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>6.3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="P7" t="n">
         <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.57</v>
@@ -1338,7 +1338,7 @@
         <v>2.25</v>
       </c>
       <c r="T7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U7" t="n">
         <v>1.22</v>
@@ -1350,13 +1350,13 @@
         <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AA7" t="n">
         <v>5.5</v>
@@ -1365,10 +1365,10 @@
         <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1377,20 +1377,20 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45796.5</v>
@@ -1407,33 +1407,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spartak Vladikavkaz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.21</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.28</v>
+        <v>3.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="U8" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.22</v>
       </c>
-      <c r="X8" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['21', '83']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['64', '66']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.35</v>
+        <v>2.25</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45796.5</v>
@@ -1665,32 +1665,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Sloven Ruma</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.62</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N10" t="n">
-        <v>2.6</v>
+        <v>6.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['-1']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>3.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['21', '83']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['64', '66']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>2.25</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45796.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Spartak Vladikavkaz</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>6.28</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.99</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>2.91</v>
       </c>
       <c r="U11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.22</v>
       </c>
-      <c r="V11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X11" t="n">
-        <v>2.4</v>
+        <v>3.52</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.63</v>
+        <v>1.89</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.44</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>2.42</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45796.5</v>
@@ -1923,32 +1923,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.92</v>
+        <v>5.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4.05</v>
+        <v>10</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.1</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="X12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['29', '67']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH12" t="n">
         <v>4.4</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['13', '23', '43']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['62', '81']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O13" t="n">
         <v>5.4</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.48</v>
       </c>
-      <c r="O13" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.15</v>
-      </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.4</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.55</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['31', '47', '70']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.63</v>
+        <v>1.96</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,49 +2217,49 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="N14" t="n">
-        <v>1.56</v>
+        <v>4.05</v>
       </c>
       <c r="O14" t="n">
-        <v>5.4</v>
+        <v>2.06</v>
       </c>
       <c r="P14" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.91</v>
+        <v>5.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X14" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA14" t="n">
         <v>2.5</v>
@@ -2268,32 +2268,32 @@
         <v>1.48</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '23', '43']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['39', '55', '87']</t>
+          <t>['62', '81']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2310,29 +2310,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.59</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.81</v>
+        <v>2.07</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.449999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.72</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['29', '67']</t>
+          <t>['21', '68', '71', '78']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.43</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>1.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>4.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.07</v>
+        <v>2.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>2.11</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['65', '77']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['3', '16', '29', '32', '39']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI16" t="n">
         <v>3.1</v>
       </c>
-      <c r="U16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['21', '68', '71', '78']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['48']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>4.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.9</v>
       </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
       <c r="N17" t="n">
-        <v>2.22</v>
+        <v>1.56</v>
       </c>
       <c r="O17" t="n">
         <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.48</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AC17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['39', '55', '87']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2.6</v>
       </c>
-      <c r="Y17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.96</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2697,35 +2697,35 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.05</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="O18" t="n">
-        <v>4.35</v>
+        <v>4.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.11</v>
+        <v>1.92</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>4.33</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['65', '77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['3', '16', '29', '32', '39']</t>
+          <t>['31', '47', '70']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45796.54166666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P19" t="n">
         <v>2.1</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.43</v>
-      </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>3.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="X19" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.47</v>
+        <v>1.91</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>3.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.81</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['47', '70']</t>
+          <t>['9', '14', '37', '43']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45796.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M21" t="n">
         <v>4</v>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['61', '87']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
         <v>2.3</v>
       </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O21" t="n">
+      <c r="AI21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.88</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['12', '47', '60', '87']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45796.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="N22" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="O22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA22" t="n">
         <v>2.1</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['39', '83']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['4', '54']</t>
+          <t>['47', '70']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45796.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['39', '83']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['4', '54']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>2.7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>['9', '14', '37', '43']</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.92</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45796.58333333334</v>
@@ -3600,119 +3600,119 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="M25" t="n">
-        <v>3.34</v>
-      </c>
       <c r="N25" t="n">
-        <v>2.26</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="T25" t="n">
-        <v>2.63</v>
+        <v>2.92</v>
       </c>
       <c r="U25" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AD25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>['12', '47', '60', '87']</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['52']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['6', '9', '32']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.8</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45796.58333333334</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.52</v>
+        <v>2.64</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>2.26</v>
       </c>
       <c r="O26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD26" t="n">
         <v>2.2</v>
       </c>
-      <c r="P26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['6', '9', '32']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['23']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>2.88</v>
+        <v>1.8</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45796.58333333334</v>
@@ -3987,32 +3987,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,65 +4023,65 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R28" t="n">
         <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V28" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
         <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD28" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2</v>
-      </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['61', '87']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AI28" t="n">
         <v>1.44</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,109 +4384,109 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S31" t="n">
         <v>4</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="M31" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="O31" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.62</v>
-      </c>
       <c r="T31" t="n">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="U31" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="V31" t="n">
         <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="X31" t="n">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.96</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.74</v>
+        <v>2.65</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.19</v>
+        <v>1.73</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['11', '40', '45+3', '70']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.07</v>
+        <v>2.72</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.98</v>
+        <v>1.46</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45796.60416666666</v>
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5</v>
+        <v>5.02</v>
       </c>
       <c r="M32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S32" t="n">
         <v>4.33</v>
       </c>
-      <c r="N32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="O32" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="V32" t="n">
         <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X32" t="n">
-        <v>5.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.41</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['23', '52', '88']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45796.60416666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,109 +4642,109 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>3</v>
       </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>5.02</v>
+        <v>2.67</v>
       </c>
       <c r="M33" t="n">
-        <v>4.2</v>
+        <v>3.03</v>
       </c>
       <c r="N33" t="n">
-        <v>1.53</v>
+        <v>2.41</v>
       </c>
       <c r="O33" t="n">
-        <v>4.75</v>
+        <v>3.42</v>
       </c>
       <c r="P33" t="n">
-        <v>2.57</v>
+        <v>2.01</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.92</v>
+        <v>3.18</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S33" t="n">
-        <v>4.33</v>
+        <v>2.62</v>
       </c>
       <c r="T33" t="n">
-        <v>1.86</v>
+        <v>3.1</v>
       </c>
       <c r="U33" t="n">
-        <v>1.88</v>
+        <v>1.32</v>
       </c>
       <c r="V33" t="n">
         <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="X33" t="n">
-        <v>7.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.96</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>3.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>1.19</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.6</v>
+        <v>1.86</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['23', '52', '88']</t>
+          <t>['11', '40', '45+3', '70']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.05</v>
+        <v>1.43</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.66</v>
+        <v>2.07</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.45</v>
+        <v>1.98</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45796.60416666666</v>
@@ -5277,35 +5277,35 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
         <v>3</v>
       </c>
-      <c r="H38" t="n">
-        <v>2</v>
-      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S38" t="n">
         <v>3.25</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4</v>
-      </c>
       <c r="T38" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="U38" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X38" t="n">
-        <v>5.25</v>
+        <v>3.96</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.25</v>
+        <v>2.79</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['32', '69', '85']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>['9', '45+1']</t>
+          <t>['48', '59', '88']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AI38" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45796.66666666666</v>
@@ -5406,119 +5406,119 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="O39" t="n">
         <v>3</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O39" t="n">
-        <v>2.63</v>
-      </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R39" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S39" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T39" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="U39" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="V39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>3.96</v>
+        <v>5.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.79</v>
+        <v>2.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '69', '85']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['48', '59', '88']</t>
+          <t>['9', '45+1']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45796.66666666666</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,23 +5545,23 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G40" t="n">
+        <v>4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="N40" t="n">
-        <v>3.23</v>
+        <v>3.86</v>
       </c>
       <c r="O40" t="n">
-        <v>3.6</v>
+        <v>2.51</v>
       </c>
       <c r="P40" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="Q40" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X40" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA40" t="n">
         <v>3.8</v>
       </c>
-      <c r="R40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X40" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>5.75</v>
-      </c>
       <c r="AB40" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['39', '71']</t>
+          <t>['22', '36', '50', '69']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45796.66666666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="N41" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O41" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['39', '71']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.44</v>
       </c>
-      <c r="S41" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['22', '36', '50', '69']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AI41" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45796.66666666666</v>
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Breidablik</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>FH</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5829,22 +5829,22 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.9</v>
+        <v>2.47</v>
       </c>
       <c r="M42" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="N42" t="n">
-        <v>3.21</v>
+        <v>2.34</v>
       </c>
       <c r="O42" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="R42" t="n">
         <v>1.2</v>
@@ -5853,59 +5853,59 @@
         <v>4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="U42" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X42" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['30', '66']</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['15', '77', '81']</t>
         </is>
       </c>
       <c r="AG42" t="n">
         <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45796.67708333334</v>
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FH</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="G44" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" t="n">
         <v>1</v>
       </c>
-      <c r="H44" t="n">
-        <v>3</v>
-      </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -6087,22 +6087,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.47</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="N44" t="n">
-        <v>2.34</v>
+        <v>3.21</v>
       </c>
       <c r="O44" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="P44" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R44" t="n">
         <v>1.2</v>
@@ -6111,59 +6111,59 @@
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="V44" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X44" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['30', '66']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['15', '77', '81']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG44" t="n">
         <v>1.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45796.67708333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G46" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
         <v>1</v>
       </c>
-      <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="O46" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="P46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X46" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AD46" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['45+4', '70']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>['7', '16']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45796.79166666666</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,25 +6448,25 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P47" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R47" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="S47" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="T47" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U47" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V47" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W47" t="n">
-        <v>1.2</v>
+        <v>1.59</v>
       </c>
       <c r="X47" t="n">
-        <v>3.7</v>
+        <v>2.35</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="Z47" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['45+4', '70']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['7', '16']</t>
+          <t>['69']</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45796.79166666666</v>
@@ -6577,22 +6577,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
         <v>2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -6603,31 +6603,31 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="M48" t="n">
-        <v>3.06</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="P48" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="R48" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S48" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="T48" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="U48" t="n">
         <v>1.3</v>
@@ -6639,47 +6639,47 @@
         <v>1.43</v>
       </c>
       <c r="X48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>['27', '38', '90+8']</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>['45+1', '46', '62']</t>
+        </is>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AJ48" t="n">
         <v>2.85</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>['4', '86']</t>
-        </is>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>2.16</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45796.8125</v>
@@ -6706,22 +6706,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ABC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6732,31 +6732,31 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.55</v>
+        <v>3.06</v>
       </c>
       <c r="N49" t="n">
-        <v>4.85</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.2</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S49" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T49" t="n">
-        <v>3.52</v>
+        <v>3.2</v>
       </c>
       <c r="U49" t="n">
         <v>1.3</v>
@@ -6768,47 +6768,47 @@
         <v>1.43</v>
       </c>
       <c r="X49" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="Y49" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AA49" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>['27', '38', '90+8']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['45+1', '46', '62']</t>
+          <t>['4', '86']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.49</v>
+        <v>1.89</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.85</v>
+        <v>2.16</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45796.8125</v>
